--- a/interviewees.xlsx
+++ b/interviewees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BB436D-7BF7-4EE4-9908-AC1443BDF194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4917448F-8626-4DCC-9B50-0637686830ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="13758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table for thesis" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="52">
   <si>
     <t>Interviewee</t>
   </si>
@@ -110,12 +110,24 @@
     <t>14</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>Interviewee number</t>
   </si>
   <si>
     <t>Interviewee real name</t>
   </si>
   <si>
+    <t>Consent</t>
+  </si>
+  <si>
     <t>Andreea Bulisache</t>
   </si>
   <si>
@@ -156,9 +168,6 @@
   </si>
   <si>
     <t>Floris Reguoin</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>Sylvia Vroklage</t>
@@ -174,17 +183,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -198,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -206,108 +208,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.6"/>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
@@ -665,550 +571,499 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A3" s="14" t="s">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A4" s="14" t="s">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="7"/>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A5" s="14" t="s">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="7"/>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A6" s="14" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="7"/>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A7" s="14" t="s">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="7"/>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A8" s="14" t="s">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="7"/>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A9" s="14" t="s">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7" t="s">
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A10" s="14" t="s">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="7"/>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A11" s="14" t="s">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A12" s="14" t="s">
+      <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A13" s="14" t="s">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A14" s="14" t="s">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A15" s="14" t="s">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A16" s="14" t="s">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A17" s="14">
-        <v>15</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A18" s="15">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A19" s="16">
-        <v>17</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.6"/>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J16 B17:G17 J17" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J19" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="2" max="2" width="27.3984375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A18" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A3" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A5" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A7" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A9" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A11" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A12" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A13" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A14" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A15" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A16" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A17" s="17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
-      <c r="A18" s="17">
-        <v>17</v>
-      </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B16" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C14 A17:C17 A15:B15 A16:B16 A18:B18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/interviewees.xlsx
+++ b/interviewees.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4917448F-8626-4DCC-9B50-0637686830ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="13758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-240" yWindow="-240" windowWidth="52080" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table for thesis" sheetId="1" r:id="rId1"/>
@@ -554,9 +554,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -602,7 +602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -616,7 +616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -630,7 +630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -650,7 +650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -664,7 +664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -678,7 +678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -692,7 +692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -703,7 +703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -717,7 +717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -731,7 +731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -773,7 +773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -818,7 +818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -863,9 +863,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -876,7 +876,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -887,7 +887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -895,7 +895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -906,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -917,7 +917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -928,7 +928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -950,7 +950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -972,7 +972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -983,7 +983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -994,7 +994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>31</v>
       </c>

--- a/interviewees.xlsx
+++ b/interviewees.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4917448F-8626-4DCC-9B50-0637686830ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="-240" windowWidth="52080" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table for thesis" sheetId="1" r:id="rId1"/>
@@ -554,9 +554,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -602,7 +602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -616,7 +616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -630,7 +630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -650,7 +650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -664,7 +664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -678,7 +678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -692,7 +692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -703,7 +703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -717,7 +717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -731,7 +731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -759,7 +759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -773,7 +773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -818,7 +818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -863,9 +863,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -876,7 +876,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -887,7 +887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -895,7 +895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -906,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -917,7 +917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -928,7 +928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -950,7 +950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -972,7 +972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -983,7 +983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -994,7 +994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
